--- a/Test Cases/Test_Cases_SauceDemo.xlsx
+++ b/Test Cases/Test_Cases_SauceDemo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nites\qa-manual-testing-portfolio\Test Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C66E53-A5D2-4E47-B920-784F52F9EEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A973A5-7B8E-463B-93B7-35EBABF39E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9BA9A7D9-0B68-4B30-B530-AA8FAAEFFCE6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="113">
   <si>
     <t>TC ID</t>
   </si>
@@ -257,64 +257,34 @@
     <t>Verify password field masks the entered password</t>
   </si>
   <si>
-    <t>TC_001</t>
-  </si>
-  <si>
     <t>User is logged in and on Products page</t>
   </si>
   <si>
     <t>Product list is displayed successfully.</t>
   </si>
   <si>
-    <t>TC_002</t>
-  </si>
-  <si>
     <t>Products page is open</t>
   </si>
   <si>
     <t>Every product displays its name correctly.</t>
   </si>
   <si>
-    <t>TC_003</t>
-  </si>
-  <si>
     <t>Product image is visible for every product and loads without broken image.</t>
   </si>
   <si>
-    <t>TC_004</t>
-  </si>
-  <si>
     <t>Every product displays the correct description.</t>
   </si>
   <si>
-    <t>TC_005</t>
-  </si>
-  <si>
     <t>Product price is displayed correctly for all products.</t>
   </si>
   <si>
-    <t>TC_006</t>
-  </si>
-  <si>
     <t>Products are sorted alphabetically from A to Z.</t>
   </si>
   <si>
-    <t>TC_007</t>
-  </si>
-  <si>
     <t>Products are sorted alphabetically from Z to A.</t>
   </si>
   <si>
-    <t>TC_008</t>
-  </si>
-  <si>
     <t>Products are sorted in ascending order of price.</t>
-  </si>
-  <si>
-    <t>TC_009</t>
-  </si>
-  <si>
-    <t>TC_010</t>
   </si>
   <si>
     <t>Product is already added to cart</t>
@@ -346,13 +316,7 @@
     </r>
   </si>
   <si>
-    <t>TC_011</t>
-  </si>
-  <si>
     <t>Cart badge count increases according to the number of added products.</t>
-  </si>
-  <si>
-    <t>TC_012</t>
   </si>
   <si>
     <t>1. Launch application.
@@ -403,13 +367,76 @@
   </si>
   <si>
     <t>All selected products are displayed in the cart with correct quantity and details.</t>
+  </si>
+  <si>
+    <t>Test Scenario ID</t>
+  </si>
+  <si>
+    <t>TS-001</t>
+  </si>
+  <si>
+    <t>TS-002</t>
+  </si>
+  <si>
+    <t>TS-003</t>
+  </si>
+  <si>
+    <t>TS-004</t>
+  </si>
+  <si>
+    <t>TS-005</t>
+  </si>
+  <si>
+    <t>TS-006</t>
+  </si>
+  <si>
+    <t>TS-007</t>
+  </si>
+  <si>
+    <t>TS-008</t>
+  </si>
+  <si>
+    <t>TS-009</t>
+  </si>
+  <si>
+    <t>TS-010</t>
+  </si>
+  <si>
+    <t>TS-011</t>
+  </si>
+  <si>
+    <t>TS-012</t>
+  </si>
+  <si>
+    <t>TS-013</t>
+  </si>
+  <si>
+    <t>TS-014</t>
+  </si>
+  <si>
+    <t>TS-015</t>
+  </si>
+  <si>
+    <t>TS-016</t>
+  </si>
+  <si>
+    <t>TS-017</t>
+  </si>
+  <si>
+    <t>TS-019</t>
+  </si>
+  <si>
+    <t>TS-018</t>
+  </si>
+  <si>
+    <t>TS-020</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -429,6 +456,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -472,21 +505,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -496,14 +519,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -819,869 +842,772 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEB91BCA-2EA0-46B9-8D41-793D9A7664FA}">
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="21.5546875" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" customWidth="1"/>
-    <col min="3" max="3" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="33.5546875" customWidth="1"/>
-    <col min="6" max="6" width="26.21875" customWidth="1"/>
-    <col min="7" max="7" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.21875" style="4" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="1" max="1" width="21.5546875" style="3" customWidth="1"/>
+    <col min="2" max="3" width="20.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="28.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30" style="3" customWidth="1"/>
+    <col min="6" max="6" width="33.5546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="26.21875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.21875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="13" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.2" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:11" ht="43.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="J2" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="K2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K2" s="5"/>
     </row>
     <row r="3" spans="1:11" ht="28.8">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
     </row>
     <row r="4" spans="1:11" ht="28.8">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
     </row>
     <row r="5" spans="1:11" ht="28.8">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:11" ht="28.8">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
     </row>
     <row r="7" spans="1:11" ht="43.2">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:11" ht="28.8">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
     </row>
     <row r="9" spans="1:11" ht="28.8">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="6" t="s">
+      <c r="C9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:11" ht="86.4" customHeight="1">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="E11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="6" t="s">
+    </row>
+    <row r="12" spans="1:11" ht="57.6" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="43.2">
+      <c r="A13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="28.8">
+      <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="28.8">
+      <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="28.8">
+      <c r="A16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="28.8">
+      <c r="A17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="28.8">
+      <c r="A18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="28.8">
+      <c r="H19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="57.6" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="43.2">
+      <c r="A21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="43.2">
+      <c r="A22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H11" s="8" t="s">
+    </row>
+    <row r="23" spans="1:9" ht="43.2">
+      <c r="A23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-    </row>
-    <row r="12" spans="1:11" ht="57.6" customHeight="1">
-      <c r="A12" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-    </row>
-    <row r="13" spans="1:11" ht="43.2">
-      <c r="A13" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" ht="28.8">
-      <c r="A14" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-    </row>
-    <row r="15" spans="1:11" ht="28.8">
-      <c r="A15" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-    </row>
-    <row r="16" spans="1:11" ht="28.8">
-      <c r="A16" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-    </row>
-    <row r="17" spans="1:11" ht="28.8">
-      <c r="A17" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-    </row>
-    <row r="18" spans="1:11" ht="28.8">
-      <c r="A18" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-    </row>
-    <row r="19" spans="1:11" ht="43.2">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-    </row>
-    <row r="20" spans="1:11" ht="57.6" customHeight="1">
-      <c r="A20" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-    </row>
-    <row r="21" spans="1:11" ht="43.2">
-      <c r="A21" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-    </row>
-    <row r="22" spans="1:11" ht="43.2">
-      <c r="A22" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-    </row>
-    <row r="23" spans="1:11" ht="43.2">
-      <c r="A23" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="1"/>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="11"/>
-      <c r="E32" s="11"/>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="E33" s="11"/>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="E34" s="11"/>
-    </row>
-    <row r="35" spans="1:5" ht="14.4" customHeight="1">
-      <c r="A35" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="11"/>
-      <c r="E35" s="11"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="11"/>
-    </row>
-    <row r="37" spans="1:5" ht="28.8" customHeight="1">
-      <c r="A37" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="11"/>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="11"/>
-    </row>
-    <row r="39" spans="1:5" ht="14.4" customHeight="1">
-      <c r="A39" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="11"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="11"/>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="11"/>
-    </row>
-    <row r="41" spans="1:5" ht="14.4" customHeight="1">
-      <c r="A41" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C41" s="11"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="11"/>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="11"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="11"/>
-    </row>
-    <row r="43" spans="1:5" ht="14.4" customHeight="1">
-      <c r="A43" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C43" s="11"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="11"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="11"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="11"/>
-    </row>
-    <row r="45" spans="1:5" ht="14.4" customHeight="1">
-      <c r="A45" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" s="11"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="11"/>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="11"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="11"/>
-    </row>
-    <row r="47" spans="1:5" ht="14.4" customHeight="1">
-      <c r="A47" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C47" s="11"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="11"/>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="11"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="11"/>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="1:5" ht="28.8">
-      <c r="A50" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C51" s="11"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="11"/>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="11"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="11"/>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="11"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="11"/>
-    </row>
-    <row r="54" spans="1:5" ht="14.4" customHeight="1">
-      <c r="A54" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C54" s="11"/>
-      <c r="D54" s="3"/>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="11"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="3"/>
+      <c r="I23" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="6"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="6"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" ht="14.4" customHeight="1">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="6"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" ht="28.8" customHeight="1">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" ht="14.4" customHeight="1">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" ht="14.4" customHeight="1">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" ht="14.4" customHeight="1">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" spans="1:6" ht="14.4" customHeight="1">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="6"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="6"/>
+    </row>
+    <row r="46" spans="1:6" ht="14.4" customHeight="1">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="6"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="6"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="6"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="6"/>
+    </row>
+    <row r="53" spans="1:6" ht="14.4" customHeight="1">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="E51:E53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="F34:F35"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
